--- a/Smoke-tests/Smoke5 - Поиск по наименованию товара.xlsx
+++ b/Smoke-tests/Smoke5 - Поиск по наименованию товара.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yaros\Documents\Smoke-tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8840A7D0-0912-4006-BE36-BF18671EDB27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A6EA229-B1CE-49A3-9C08-405001FC2EFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8490" yWindow="3285" windowWidth="23160" windowHeight="11685" xr2:uid="{60CBE097-ABDC-4BE2-8156-EB43CE3551D6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{60CBE097-ABDC-4BE2-8156-EB43CE3551D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -85,12 +85,6 @@
 3) Открыт главный экран</t>
   </si>
   <si>
-    <t>В поле поиска выбрать "Поиск по товарам"</t>
-  </si>
-  <si>
-    <t>Ввести название товара в поле</t>
-  </si>
-  <si>
     <t>Кирпич</t>
   </si>
   <si>
@@ -100,10 +94,16 @@
     <t>Поле принимает введенное значение</t>
   </si>
   <si>
-    <t>Нажать на клавишу "Enter" или лупу</t>
-  </si>
-  <si>
     <t>Отображаются товары соответствующие названию(в данном случае кирпичи)</t>
+  </si>
+  <si>
+    <t>1) В поле поиска выбрать "Поиск по товарам"</t>
+  </si>
+  <si>
+    <t>2) Ввести название товара в поле</t>
+  </si>
+  <si>
+    <t>3) Нажать на клавишу "Enter" или лупу</t>
   </si>
 </sst>
 </file>
@@ -680,11 +680,11 @@
         <v>14</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G2" s="6"/>
       <c r="H2" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I2" s="7" t="s">
         <v>11</v>
@@ -697,13 +697,13 @@
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
       <c r="F3" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G3" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="6" t="s">
         <v>17</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>19</v>
       </c>
       <c r="I3" s="7"/>
     </row>
@@ -714,11 +714,11 @@
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
       <c r="F4" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I4" s="7"/>
     </row>
